--- a/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
+++ b/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1936,6 +1936,58 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>I-6610</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-8.0896773</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-79.0893202</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Avenida Ramón Castilla / Calle César Vallejo</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>130101</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
+++ b/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,12 +518,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida Pumacahua / Avenida Julian Arce</t>
+          <t>Avenida Julian Arce / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -639,12 +639,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I-41573</t>
+          <t>I-54204</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>130102</t>
+          <t>130106</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -659,22 +659,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EL PORVENIR</t>
+          <t>LAREDO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-8.086945</t>
+          <t>-8.0923354</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-79.002148</t>
+          <t>-78.9562538</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida José Faustino Sánchez Carrión / Avenida Pumacahua</t>
+          <t>Avenida Trujillo / Calle Zarumilla</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I-54204</t>
+          <t>I-828495</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>130106</t>
+          <t>130107</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -711,22 +711,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LAREDO</t>
+          <t>MOCHE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-8.0923354</t>
+          <t>-8.150675</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-78.9562538</t>
+          <t>-79.010571</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avenida Trujillo / Calle Zarumilla</t>
+          <t>Calle Entrada a La Campiña / Calle Entrada a la Campiña / Pasaje Las Flores</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -743,12 +743,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I-828495</t>
+          <t>I-335601</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130107</t>
+          <t>130106</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -763,27 +763,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MOCHE</t>
+          <t>LAREDO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-8.150675</t>
+          <t>-8.0926672</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-79.010571</t>
+          <t>-78.9651105</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pasaje Las Flores / Calle Entrada a La Campiña</t>
+          <t>Avenida Julian Arce / Avenida Trujillo</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -795,12 +795,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I-335601</t>
+          <t>I-312831</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>130106</t>
+          <t>130101</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -815,27 +815,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LAREDO</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-8.0926672</t>
+          <t>-8.1230718</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-78.9651105</t>
+          <t>-79.0226551</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida Trujillo / Calle s / n</t>
+          <t>Avenida América Sur / Plaza Miguel Grau</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -847,12 +847,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I-312831</t>
+          <t>I-291540</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>130101</t>
+          <t>130104</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -867,27 +867,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>HUANCHACO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-8.1230718</t>
+          <t>-8.0718011</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-79.0226551</t>
+          <t>-79.1136787</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Avenida América Sur / Calle s / n</t>
+          <t>Avenida Cerrito de la Virgen / Calle s / n</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -899,12 +899,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I-291540</t>
+          <t>I-39877</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>130104</t>
+          <t>130106</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -919,22 +919,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HUANCHACO</t>
+          <t>LAREDO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-8.0718011</t>
+          <t>-8.0878192</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-79.1136787</t>
+          <t>-78.9815497</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Avenida Cerrito de la Virgen / Calle s / n</t>
+          <t>Avenida Pumacahua / Calle s / n</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -951,12 +951,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I-39877</t>
+          <t>I-40656</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>130106</t>
+          <t>130107</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -971,22 +971,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LAREDO</t>
+          <t>MOCHE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-8.0878192</t>
+          <t>-8.1660152</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-78.9815497</t>
+          <t>-79.0218291</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Avenida Pumacahua / Calle s / n</t>
+          <t>Avenida Las Américas / Calle s / n</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1003,12 +1003,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I-40656</t>
+          <t>I-436170</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>130107</t>
+          <t>130104</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1023,22 +1023,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MOCHE</t>
+          <t>HUANCHACO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-8.1660152</t>
+          <t>-8.0881171</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-79.0218291</t>
+          <t>-79.093799</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Avenida Las Américas / Calle s / n</t>
+          <t>Avenida Ramón Castilla / Calle s / n</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1055,12 +1055,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I-436170</t>
+          <t>I-35571</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>130104</t>
+          <t>130101</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1075,22 +1075,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HUANCHACO</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-8.0881171</t>
+          <t>-8.1165661</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-79.093799</t>
+          <t>-79.0165503</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Avenida Ramón Castilla / Calle s / n</t>
+          <t>Avenida América Sur / Jirón Francisco de Zela</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1107,12 +1107,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I-35571</t>
+          <t>I-474460</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>130101</t>
+          <t>130107</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1127,22 +1127,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>MOCHE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-8.1165661</t>
+          <t>-8.1776568</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-79.0165503</t>
+          <t>-79.0122847</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Avenida América Sur / Jirón Francisco de Zela</t>
+          <t>Avenida Independencia / Calle s / n</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1159,7 +1159,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I-474460</t>
+          <t>I-496147</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-8.1776568</t>
+          <t>-8.1506716</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-79.0122847</t>
+          <t>-79.0100382</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Avenida Independencia / Calle s / n</t>
+          <t>Calle Entrada a la Campiña / Calle s / n</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1211,12 +1211,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I-496147</t>
+          <t>I-38514</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>130107</t>
+          <t>130101</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1231,22 +1231,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MOCHE</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-8.1506716</t>
+          <t>-8.0935094</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-79.0100382</t>
+          <t>-78.9962529</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Calle Entrada a la Campiña / Calle s / n</t>
+          <t>Avenida Libertad / Avenida Pesqueda</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1263,7 +1263,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I-38514</t>
+          <t>I-40521</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1288,17 +1288,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-8.0935094</t>
+          <t>-8.0879657</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-78.9962529</t>
+          <t>-79.0395057</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Avenida Libertad / Avenida Pesqueda</t>
+          <t>Avenida Túpac Amaru / Calle Trujillo</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I-40521</t>
+          <t>I-41543</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1340,17 +1340,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-8.0879657</t>
+          <t>-8.1120207</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-79.0395057</t>
+          <t>-79.0328614</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru / Calle Trujillo</t>
+          <t>Avenida España / Pasaje San Luis</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I-41543</t>
+          <t>I-41879</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1392,17 +1392,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-8.1120207</t>
+          <t>-8.0857802</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-79.0328614</t>
+          <t>-79.015652</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Avenida España / Pasaje San Luis</t>
+          <t>Avenida 26 de Marzo / Avenida los Laureles / Pasaje Laureles</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I-41879</t>
+          <t>I-42485</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-8.0857802</t>
+          <t>-8.1198975</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-79.015652</t>
+          <t>-79.028712</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Avenida los Laureles / Pasaje Laureles</t>
+          <t>Avenida 29 de Diciembre / Calle Paraguay</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1471,12 +1471,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I-42485</t>
+          <t>I-42699</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>130101</t>
+          <t>130107</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1491,22 +1491,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>MOCHE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-8.1198975</t>
+          <t>-8.1632939</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-79.028712</t>
+          <t>-79.0045719</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Avenida 29 de Diciembre / Calle Paraguay</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I-42699</t>
+          <t>I-828494</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1548,17 +1548,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-8.1632939</t>
+          <t>-8.166455</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-79.0045719</t>
+          <t>-79.020787</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Las Américas / Calle s / n</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1575,12 +1575,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I-828494</t>
+          <t>I-6571</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>130107</t>
+          <t>130104</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1595,22 +1595,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MOCHE</t>
+          <t>HUANCHACO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-8.166455</t>
+          <t>-8.0877653</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-79.020787</t>
+          <t>-79.0952007</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Av. Las Americas / Calle s / n</t>
+          <t>Avenida Ramón Castilla / Calle Remanso</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1627,12 +1627,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I-6571</t>
+          <t>I-440446</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>130104</t>
+          <t>130101</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1647,27 +1647,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>HUANCHACO</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-8.0877653</t>
+          <t>-8.0907051</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-79.0952007</t>
+          <t>-79.0366434</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Avenida Ramón Castilla / Calle s / n</t>
+          <t>Avenida Túpac Amaru / Calle s / n</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>I-440446</t>
+          <t>I-585458</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>130101</t>
+          <t>130104</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1699,22 +1699,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>HUANCHACO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-8.0907051</t>
+          <t>-8.0656234</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-79.0366434</t>
+          <t>-79.1085058</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1731,12 +1731,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>I-585458</t>
+          <t>I-543884</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>130104</t>
+          <t>130107</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1751,17 +1751,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HUANCHACO</t>
+          <t>MOCHE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-8.0656234</t>
+          <t>-8.156657</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-79.1085058</t>
+          <t>-79.0261364</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1783,7 +1783,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>I-543884</t>
+          <t>I-224603</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-8.156657</t>
+          <t>-8.1689397</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-79.0261364</t>
+          <t>-79.0121859</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1835,7 +1835,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>I-224603</t>
+          <t>I-224609</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1860,17 +1860,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-8.1689397</t>
+          <t>-8.1650205</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-79.0121859</t>
+          <t>-79.0251149</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Las Américas / Calle s / n</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1887,12 +1887,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>I-224609</t>
+          <t>I-6610</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>130107</t>
+          <t>130104</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1907,22 +1907,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MOCHE</t>
+          <t>HUANCHACO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-8.1650205</t>
+          <t>-8.0896773</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-79.0251149</t>
+          <t>-79.0893202</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Avenida Las Américas / Calle s / n</t>
+          <t>Avenida Ramón Castilla / Calle César Vallejo</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1939,7 +1939,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>I-6610</t>
+          <t>I-6612</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1964,17 +1964,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-8.0896773</t>
+          <t>-8.0885519</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-79.0893202</t>
+          <t>-79.0927291</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Avenida Ramón Castilla / Calle César Vallejo</t>
+          <t>Avenida Ramón Castilla / Calle s / n</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1983,6 +1983,214 @@
         </is>
       </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t>130101</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>I-7274</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>130106</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>LAREDO</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-8.0852643</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-78.9869583</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Avenida Pumacahua / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>130101</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>I-646855</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>130107</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>MOCHE</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-8.1491752</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-79.008207</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Calle Entrada a la Campiña / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>130101</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>I-646853</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>130107</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>MOCHE</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-8.149082</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-79.0085781</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>130101</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>I-6509</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>130111</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>VICTOR LARCO HERRERA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-8.1306032</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-79.0440852</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Avenida Victor Larco Herrera / Calle las Casuarinas / Calle los Tilos</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>130101</t>
         </is>

--- a/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
+++ b/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-236847</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>130106</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>LAREDO</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-8.0926598</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-33889</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>130111</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>VICTOR LARCO HERRERA</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-8.1291328</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-340081</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>130111</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>VICTOR LARCO HERRERA</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-8.1293843</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-54204</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>130106</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>LAREDO</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-8.0923354</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-828495</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>130107</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>MOCHE</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-8.150675</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-335601</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>130106</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LAREDO</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-8.0926672</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-312831</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>130101</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-8.1230718</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-291540</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-8.0718011</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-39877</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>130106</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>LAREDO</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-8.0878192</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-40656</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>130107</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MOCHE</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-8.1660152</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-436170</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-8.0881171</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-35571</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>130101</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-8.1165661</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-474460</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>130107</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MOCHE</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-8.1776568</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-496147</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>130107</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MOCHE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-8.1506716</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-38514</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>130101</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-8.0935094</t>
@@ -1252,40 +1177,35 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>I-40521</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>130101</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-8.0879657</t>
@@ -1304,40 +1224,35 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>I-41543</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>130101</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-8.1120207</t>
@@ -1356,40 +1271,35 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>I-41879</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>130101</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-8.0857802</t>
@@ -1408,40 +1318,35 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>I-42485</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>130101</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-8.1198975</t>
@@ -1460,40 +1365,35 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>I-42699</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>130107</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>MOCHE</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-8.1632939</t>
@@ -1512,40 +1412,35 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>I-828494</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>130107</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>MOCHE</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-8.166455</t>
@@ -1564,40 +1459,35 @@
       <c r="I22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>I-6571</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-8.0877653</t>
@@ -1616,40 +1506,35 @@
       <c r="I23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>I-440446</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>130101</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-8.0907051</t>
@@ -1668,40 +1553,35 @@
       <c r="I24" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>I-585458</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-8.0656234</t>
@@ -1720,40 +1600,35 @@
       <c r="I25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>I-543884</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>130107</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>MOCHE</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>-8.156657</t>
@@ -1772,40 +1647,35 @@
       <c r="I26" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>I-224603</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>130107</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>MOCHE</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>-8.1689397</t>
@@ -1824,40 +1694,35 @@
       <c r="I27" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>I-224609</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>130107</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>MOCHE</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>-8.1650205</t>
@@ -1876,40 +1741,35 @@
       <c r="I28" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>I-6610</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>-8.0896773</t>
@@ -1928,40 +1788,35 @@
       <c r="I29" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>I-6612</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>-8.0885519</t>
@@ -1980,40 +1835,35 @@
       <c r="I30" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>I-7274</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>130106</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>LAREDO</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>-8.0852643</t>
@@ -2032,40 +1882,35 @@
       <c r="I31" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>I-646855</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>130107</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>MOCHE</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>-8.1491752</t>
@@ -2084,40 +1929,35 @@
       <c r="I32" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>I-646853</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>130107</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>MOCHE</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>-8.149082</t>
@@ -2136,40 +1976,35 @@
       <c r="I33" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>I-6509</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>130111</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>VICTOR LARCO HERRERA</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>-8.1306032</t>
@@ -2188,11 +2023,6 @@
       <c r="I34" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
+++ b/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
+++ b/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">

--- a/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
+++ b/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
+++ b/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
@@ -486,22 +486,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-236847</t>
+          <t>I-828495</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-8.0926598</t>
+          <t>-8.150675</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-78.9674968</t>
+          <t>-79.010571</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida Julian Arce / Calle s / n</t>
+          <t>Pasaje Las Flores / Calle Entrada a La Campiña</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -533,27 +533,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-33889</t>
+          <t>I-828494</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-8.1291328</t>
+          <t>-8.166455</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-79.0427043</t>
+          <t>-79.020787</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida Victor Larco Herrera / Juan J. Ganoza</t>
+          <t>Av. Las Americas / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -580,27 +580,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-340081</t>
+          <t>I-7274</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-8.1293843</t>
+          <t>-8.0852643</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-79.0429224</t>
+          <t>-78.9869583</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida Victor Larco Herrera / Calle s / n</t>
+          <t>Avenida Pumacahua / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -627,27 +627,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-54204</t>
+          <t>I-6612</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-8.0923354</t>
+          <t>-8.0885519</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-78.9562538</t>
+          <t>-79.0927291</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Trujillo / Calle Zarumilla</t>
+          <t>Avenida Ramón Castilla / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -674,27 +674,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-828495</t>
+          <t>I-6610</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-8.150675</t>
+          <t>-8.0896773</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-79.010571</t>
+          <t>-79.0893202</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Calle Entrada a La Campiña / Calle Entrada a la Campiña / Pasaje Las Flores</t>
+          <t>Avenida Ramón Castilla / Calle César Vallejo</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-335601</t>
+          <t>I-6571</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-8.0926672</t>
+          <t>-8.0877653</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-78.9651105</t>
+          <t>-79.0952007</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Avenida Julian Arce / Avenida Trujillo</t>
+          <t>Avenida Ramón Castilla / Calle s / n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-312831</t>
+          <t>I-6509</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-8.1230718</t>
+          <t>-8.1306032</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-79.0226551</t>
+          <t>-79.0440852</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida América Sur / Plaza Miguel Grau</t>
+          <t>Avenida Victor Larco Herrera / Calle las Casuarinas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -815,27 +815,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-291540</t>
+          <t>I-646855</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-8.0718011</t>
+          <t>-8.1491752</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-79.1136787</t>
+          <t>-79.008207</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Avenida Cerrito de la Virgen / Calle s / n</t>
+          <t>Calle Entrada a la Campiña / Calle s / n</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -862,27 +862,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-39877</t>
+          <t>I-646853</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-8.0878192</t>
+          <t>-8.149082</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-78.9815497</t>
+          <t>-79.0085781</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Avenida Pumacahua / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -909,27 +909,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-40656</t>
+          <t>I-585458</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-8.1660152</t>
+          <t>-8.0656234</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-79.0218291</t>
+          <t>-79.1085058</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Avenida Las Américas / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -956,27 +956,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-436170</t>
+          <t>I-543884</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-8.0881171</t>
+          <t>-8.156657</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-79.093799</t>
+          <t>-79.0261364</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Avenida Ramón Castilla / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1003,22 +1003,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-35571</t>
+          <t>I-54204</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-8.1165661</t>
+          <t>-8.0923354</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-79.0165503</t>
+          <t>-78.9562538</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Avenida América Sur / Jirón Francisco de Zela</t>
+          <t>Avenida Trujillo / Calle Zarumilla</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1050,22 +1050,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-474460</t>
+          <t>I-496147</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-8.1776568</t>
+          <t>-8.1506716</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-79.0122847</t>
+          <t>-79.0100382</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Avenida Independencia / Calle s / n</t>
+          <t>Calle Entrada a la Campiña / Calle s / n</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1097,22 +1097,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-496147</t>
+          <t>I-474460</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-8.1506716</t>
+          <t>-8.1776568</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-79.0100382</t>
+          <t>-79.0122847</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Calle Entrada a la Campiña / Calle s / n</t>
+          <t>Avenida Independencia / Calle s / n</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1144,22 +1144,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-38514</t>
+          <t>I-440446</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-8.0935094</t>
+          <t>-8.0907051</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-78.9962529</t>
+          <t>-79.0366434</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Avenida Libertad / Avenida Pesqueda</t>
+          <t>Avenida Túpac Amaru / Calle s / n</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1191,22 +1191,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-40521</t>
+          <t>I-436170</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-8.0879657</t>
+          <t>-8.0881171</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-79.0395057</t>
+          <t>-79.093799</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru / Calle Trujillo</t>
+          <t>Avenida Ramón Castilla / Calle s / n</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1238,22 +1238,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-41543</t>
+          <t>I-42699</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-8.1120207</t>
+          <t>-8.1632939</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-79.0328614</t>
+          <t>-79.0045719</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Avenida España / Pasaje San Luis</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1285,22 +1285,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I-41879</t>
+          <t>I-42485</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-8.0857802</t>
+          <t>-8.1198975</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-79.015652</t>
+          <t>-79.028712</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Avenida 26 de Marzo / Avenida los Laureles / Pasaje Laureles</t>
+          <t>Avenida 29 de Diciembre / Calle Paraguay</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1332,22 +1332,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I-42485</t>
+          <t>I-41879</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-8.1198975</t>
+          <t>-8.0857802</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-79.028712</t>
+          <t>-79.015652</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Avenida 29 de Diciembre / Calle Paraguay</t>
+          <t>Avenida los Laureles / Pasaje Laureles</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1379,22 +1379,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I-42699</t>
+          <t>I-41543</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-8.1632939</t>
+          <t>-8.1120207</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-79.0045719</t>
+          <t>-79.0328614</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida España / Pasaje San Luis</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>I-828494</t>
+          <t>I-40656</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-8.166455</t>
+          <t>-8.1660152</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-79.020787</t>
+          <t>-79.0218291</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1473,27 +1473,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>I-6571</t>
+          <t>I-40521</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-8.0877653</t>
+          <t>-8.0879657</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-79.0952007</t>
+          <t>-79.0395057</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Avenida Ramón Castilla / Calle Remanso</t>
+          <t>Avenida Túpac Amaru / Calle Trujillo</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1520,22 +1520,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>I-440446</t>
+          <t>I-39877</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-8.0907051</t>
+          <t>-8.0878192</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-79.0366434</t>
+          <t>-78.9815497</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru / Calle s / n</t>
+          <t>Avenida Pumacahua / Calle s / n</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1567,27 +1567,27 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>I-585458</t>
+          <t>I-38514</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-8.0656234</t>
+          <t>-8.0935094</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-79.1085058</t>
+          <t>-78.9962529</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Libertad / Avenida Pesqueda</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1614,27 +1614,27 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>I-543884</t>
+          <t>I-35571</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-8.156657</t>
+          <t>-8.1165661</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-79.0261364</t>
+          <t>-79.0165503</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida América Sur / Jirón Francisco de Zela</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1661,27 +1661,27 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>I-224603</t>
+          <t>I-340081</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-8.1689397</t>
+          <t>-8.1293843</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-79.0121859</t>
+          <t>-79.0429224</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Victor Larco Herrera / Calle s / n</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1708,27 +1708,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>I-224609</t>
+          <t>I-33889</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-8.1650205</t>
+          <t>-8.1291328</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-79.0251149</t>
+          <t>-79.0427043</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Avenida Las Américas / Calle s / n</t>
+          <t>Avenida Victor Larco Herrera / Juan J. Ganoza</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1755,22 +1755,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>I-6610</t>
+          <t>I-335601</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-8.0896773</t>
+          <t>-8.0926672</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-79.0893202</t>
+          <t>-78.9651105</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Avenida Ramón Castilla / Calle César Vallejo</t>
+          <t>Avenida Trujillo / Calle s / n</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1802,27 +1802,27 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>I-6612</t>
+          <t>I-312831</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-8.0885519</t>
+          <t>-8.1230718</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-79.0927291</t>
+          <t>-79.0226551</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Avenida Ramón Castilla / Calle s / n</t>
+          <t>Avenida América Sur / Calle s / n</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1849,27 +1849,27 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>I-7274</t>
+          <t>I-291540</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-8.0852643</t>
+          <t>-8.0718011</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-78.9869583</t>
+          <t>-79.1136787</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Avenida Pumacahua / Calle s / n</t>
+          <t>Avenida Cerrito de la Virgen / Calle s / n</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1896,27 +1896,27 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>I-646855</t>
+          <t>I-236847</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-8.1491752</t>
+          <t>-8.0926598</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-79.008207</t>
+          <t>-78.9674968</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Calle Entrada a la Campiña / Calle s / n</t>
+          <t>Avenida Pumacahua / Avenida Julian Arce</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1943,22 +1943,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>I-646853</t>
+          <t>I-224609</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-8.149082</t>
+          <t>-8.1650205</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-79.0085781</t>
+          <t>-79.0251149</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Las Américas / Calle s / n</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1990,22 +1990,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>I-6509</t>
+          <t>I-224603</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-8.1306032</t>
+          <t>-8.1689397</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-79.0440852</t>
+          <t>-79.0121859</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Avenida Victor Larco Herrera / Calle las Casuarinas / Calle los Tilos</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
